--- a/templates/samples/SALES_EDGE_CASES.xlsx
+++ b/templates/samples/SALES_EDGE_CASES.xlsx
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>nw</v>
+        <v>Date</v>
       </c>
       <c r="B1" t="str">
         <v>Order Number</v>
